--- a/샘플출력_확인용.xlsx
+++ b/샘플출력_확인용.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>일일 작업계획서 점검 결과 보고</t>
   </si>
@@ -31,7 +31,7 @@
     <t>2026년 8월 28일</t>
   </si>
   <si>
-    <t>광주학동4구역 재개발현장</t>
+    <t>아이파크무등산스카이포레</t>
   </si>
   <si>
     <t xml:space="preserve">    안전점검 사진 대지</t>
@@ -62,12 +62,6 @@
   <si>
     <t xml:space="preserve">내용 : [삼마도건]
 거푸집 설치작업자 특별안전교육 실시</t>
-  </si>
-  <si>
-    <t>내용 : 작업시 근로자 안전대 착용 확인</t>
-  </si>
-  <si>
-    <t>내용 : 단부구간 작업시 안전고리 체결 확인</t>
   </si>
 </sst>
 </file>
@@ -887,138 +881,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3308,12 +3170,10 @@
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
-      <c r="G20" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
       <c r="K20" s="6"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3322,10 +3182,10 @@
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
       <c r="K21" s="6"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3334,10 +3194,10 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
       <c r="K22" s="6"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3532,42 +3392,38 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
-      <c r="B39" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="G39" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
       <c r="K39" s="6"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
       <c r="K40" s="6"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
       <c r="K41" s="6"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
